--- a/DATAFiles/Ch02/DATAfiles/softdrink.xlsx
+++ b/DATAFiles/Ch02/DATAfiles/softdrink.xlsx
@@ -1,21 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikef\Dropbox\ASW Files\MBS\MBS 8e\_First Drafts\Chapter 2 Descriptive Statistics Tabular and Graphical - Fry\DATAfiles\notcamelcase\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h69j985\Documents\GitHub\BMGT-204IS\DATAFiles\Ch02\DATAfiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10CF4090-46B1-4B07-B582-AFBFBAECCE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D33518-0929-4E63-9B44-1B88AB4D7E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29970" yWindow="945" windowWidth="19665" windowHeight="15255" xr2:uid="{6E6F4AD7-C20D-47DD-806D-4285CB0904F3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E6F4AD7-C20D-47DD-806D-4285CB0904F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$C$2:$C$7</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$D$1</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$D$2:$D$7</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$C$2:$C$7</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$D$1</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$D$2:$D$7</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="9" r:id="rId2"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="10">
   <si>
     <t>Brand Purchased</t>
   </si>
@@ -54,6 +65,18 @@
   </si>
   <si>
     <t>Sprite</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Count of Brand Purchased</t>
+  </si>
+  <si>
+    <t>Precent Frequency</t>
+  </si>
+  <si>
+    <t>Relative Frequncy</t>
   </si>
 </sst>
 </file>
@@ -101,10 +124,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -122,10 +151,1426 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[softdrink.xlsx]Sheet1!PivotTable2</c:name>
+    <c:fmtId val="1"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count of Brand Purchased</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$2:$C$7</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Coca-Cola</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Diet Coke</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Dr. Pepper</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Pepsi</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Sprite</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$2:$D$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-ADDF-425D-91FF-153DC6B3D422}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Precent Frequency</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$2:$C$7</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Coca-Cola</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Diet Coke</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Dr. Pepper</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Pepsi</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Sprite</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.38</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-ADDF-425D-91FF-153DC6B3D422}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1184875008"/>
+        <c:axId val="1198245679"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1184875008"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1198245679"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1198245679"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1184875008"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>5715</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>132397</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1005840</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>160972</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2ED4429-3521-9AD6-D972-DDB9B6AB464D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Swift, Xuying" refreshedDate="46268.457463194442" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="50" xr:uid="{0590DF92-3BE3-464A-84FB-223A30A45C6A}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:A51" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="1">
+    <cacheField name="Brand Purchased" numFmtId="0">
+      <sharedItems count="5">
+        <s v="Coca-Cola"/>
+        <s v="Diet Coke"/>
+        <s v="Pepsi"/>
+        <s v="Dr. Pepper"/>
+        <s v="Sprite"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="50">
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{99A7662E-99F3-4A02-B5AF-A69515D91D2E}" name="PivotTable2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Brand Purchased">
+  <location ref="C1:E7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="1">
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Count of Brand Purchased" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Precent Frequency" fld="0" subtotal="count" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -163,7 +1608,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -269,7 +1714,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -411,7 +1856,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -419,268 +1864,366 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448D96C7-75B9-4270-AA26-712BDA0F6033}">
-  <dimension ref="A1:A51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>19</v>
+      </c>
+      <c r="E2" s="6">
+        <v>0.38</v>
+      </c>
+      <c r="F2">
+        <f>D2/$D$7</f>
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>8</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F6" si="0">D3/$D$7</f>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5">
+        <v>5</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5">
+        <v>13</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.26</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5">
+        <v>5</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="5">
+        <v>50</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <f>SUM(F2:F6)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>